--- a/examples/templates/docuskills_template.xlsx
+++ b/examples/templates/docuskills_template.xlsx
@@ -22,6 +22,8 @@
     <definedName name="period">'Cover'!$B$5</definedName>
     <definedName name="report_subtitle">'Cover'!$A$2</definedName>
     <definedName name="report_title">'Cover'!$A$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Cover'!$A$1:$E$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Model'!$A$1:$G$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,7 +37,7 @@
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="167" formatCode="_($* #,##0_);_($* (#,##0);_($* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,6 +66,12 @@
       <name val="Calibri"/>
       <color rgb="FF2B7CD3"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="20"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -132,20 +140,22 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="2"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="5"/>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="5"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="4"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -274,6 +284,9 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2B7CD3"/>
+            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
@@ -285,64 +298,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Model'!$B$7</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Model'!$B$3:$E$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Model'!$C$7</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Model'!$B$3:$E$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Model'!$D$7</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Model'!$B$3:$E$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Model'!$E$7</f>
+              <f>'Model'!$B$7:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -355,6 +311,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -366,16 +323,15 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -394,7 +350,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>FY total by line item</a:t>
+              <a:t>Net revenue trend (Q1-Q4)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -407,12 +363,13 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <strRef>
-              <f>'Model'!F3</f>
-            </strRef>
+            <v>Net revenue</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="E0742B"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -424,11 +381,17 @@
               </a:ln>
             </spPr>
           </marker>
+          <cat>
+            <numRef>
+              <f>'Model'!$B$3:$E$3</f>
+            </numRef>
+          </cat>
           <val>
             <numRef>
-              <f>'Model'!$F$4:$F$7</f>
+              <f>'Model'!$B$7:$E$7</f>
             </numRef>
           </val>
+          <smooth val="0"/>
         </ser>
         <axId val="10"/>
         <axId val="100"/>
@@ -438,6 +401,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -449,15 +413,17 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -469,12 +435,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>6</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>0</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="914400" cy="342900"/>
+    <ext cx="609600" cy="609600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -499,12 +465,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="5040000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -526,12 +492,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>3</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="5040000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -852,26 +818,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>{{report_title}}</t>
+          <t>FY2025 Revenue Performance Review</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>{{report_subtitle}}</t>
+          <t>Quarterly revenue model and executive summary</t>
         </is>
       </c>
     </row>
@@ -883,7 +849,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{{client_name}}</t>
+          <t>DocuSkills Corp (synthetic demo)</t>
         </is>
       </c>
     </row>
@@ -895,7 +861,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{{period}}</t>
+          <t>FY2025 (Q1-Q4)</t>
         </is>
       </c>
     </row>
@@ -911,12 +877,21 @@
         </is>
       </c>
     </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -935,84 +910,84 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Model Inputs</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Driver</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Units sold</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="B4" s="8" t="n">
+        <v>29070</v>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>ea</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Unit price</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="B5" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Discount rate</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="10" t="n">
         <v>0.12</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>pct</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="10" t="n">
         <v>0.22</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>pct</t>
         </is>
@@ -1027,59 +1002,59 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Revenue Model</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Line item</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>FY Total</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>% of FY</t>
         </is>
@@ -1091,23 +1066,23 @@
           <t>Gross revenue</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n">
+      <c r="B4" s="11" t="n">
         <v>320000</v>
       </c>
-      <c r="C4" s="9" t="n">
+      <c r="C4" s="11" t="n">
         <v>351000</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="11" t="n">
         <v>372500</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="11" t="n">
         <v>410000</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="11">
         <f>SUM(B4:E4)</f>
         <v/>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="12">
         <f>IF($F$7=0,0,F4/$F$7)</f>
         <v/>
       </c>
@@ -1118,23 +1093,23 @@
           <t>Discounts</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="11" t="n">
         <v>-38400</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="11" t="n">
         <v>-42120</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="11" t="n">
         <v>-44700</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="11" t="n">
         <v>-49200</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="11">
         <f>SUM(B5:E5)</f>
         <v/>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="12">
         <f>IF($F$7=0,0,F5/$F$7)</f>
         <v/>
       </c>
@@ -1145,23 +1120,23 @@
           <t>Returns</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="11" t="n">
         <v>-9600</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="11" t="n">
         <v>-10530</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="11" t="n">
         <v>-11175</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="11" t="n">
         <v>-12300</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="11">
         <f>SUM(B6:E6)</f>
         <v/>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="12">
         <f>IF($F$7=0,0,F6/$F$7)</f>
         <v/>
       </c>
@@ -1172,27 +1147,27 @@
           <t>Net revenue</t>
         </is>
       </c>
-      <c r="B7">
+      <c r="B7" s="11">
         <f>SUM(B4:B6)</f>
         <v/>
       </c>
-      <c r="C7">
+      <c r="C7" s="11">
         <f>SUM(C4:C6)</f>
         <v/>
       </c>
-      <c r="D7">
+      <c r="D7" s="11">
         <f>SUM(D4:D6)</f>
         <v/>
       </c>
-      <c r="E7">
+      <c r="E7" s="11">
         <f>SUM(E4:E6)</f>
         <v/>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="11">
         <f>SUM(B7:E7)</f>
         <v/>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="12">
         <f>IF($F$7=0,0,F7/$F$7)</f>
         <v/>
       </c>
@@ -1203,7 +1178,7 @@
           <t>Subtotal (visible)</t>
         </is>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="11">
         <f>SUBTOTAL(9,F4:F6)</f>
         <v/>
       </c>
@@ -1232,6 +1207,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
@@ -1243,7 +1219,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1253,19 +1229,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Executive Summary</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -1277,7 +1253,7 @@
           <t>FY net revenue</t>
         </is>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="11">
         <f>Model!F7</f>
         <v/>
       </c>
@@ -1288,7 +1264,7 @@
           <t>Units sold (input)</t>
         </is>
       </c>
-      <c r="B5">
+      <c r="B5" s="11">
         <f>Inputs!B4</f>
         <v/>
       </c>
@@ -1299,7 +1275,7 @@
           <t>Unit price (input)</t>
         </is>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="9">
         <f>Inputs!B5</f>
         <v/>
       </c>
@@ -1310,7 +1286,7 @@
           <t>Implied gross</t>
         </is>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="9">
         <f>Inputs!B4*Inputs!B5</f>
         <v/>
       </c>
@@ -1321,7 +1297,7 @@
           <t>Net margin</t>
         </is>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="10">
         <f>IF(B7=0,0,B4/B7)</f>
         <v/>
       </c>
@@ -1334,12 +1310,13 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{{headline_kpi}}</t>
+          <t>85% net margin on $1.45M gross</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -1360,22 +1337,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
@@ -1397,7 +1374,7 @@
           <t>Widget</t>
         </is>
       </c>
-      <c r="D2" s="11" t="n">
+      <c r="D2" s="13" t="n">
         <v>12500</v>
       </c>
     </row>
@@ -1417,7 +1394,7 @@
           <t>Gadget</t>
         </is>
       </c>
-      <c r="D3" s="11" t="n">
+      <c r="D3" s="13" t="n">
         <v>9800</v>
       </c>
     </row>
@@ -1437,7 +1414,7 @@
           <t>Widget</t>
         </is>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="D4" s="13" t="n">
         <v>14200</v>
       </c>
     </row>
@@ -1447,7 +1424,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="11">
         <f>SUM(D2:D4)</f>
         <v/>
       </c>
